--- a/owlcms/src/main/resources/iwf/IWFCategories.xlsx
+++ b/owlcms/src/main/resources/iwf/IWFCategories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\iwf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC469376-37FF-4BAD-82B7-2FD21C84F1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D777EE18-C110-4842-94F2-DFD032E2DEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2865" yWindow="2415" windowWidth="24615" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>M</t>
   </si>
   <si>
-    <t>M109</t>
-  </si>
-  <si>
     <t>M999</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
     <t>M88</t>
   </si>
   <si>
-    <t>M98</t>
-  </si>
-  <si>
     <t>F44</t>
   </si>
   <si>
@@ -95,6 +89,12 @@
   </si>
   <si>
     <t>Youth?</t>
+  </si>
+  <si>
+    <t>M94</t>
+  </si>
+  <si>
+    <t>M110</t>
   </si>
 </sst>
 </file>
@@ -544,20 +544,20 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2"/>
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>4</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
@@ -612,7 +612,7 @@
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>4</v>
@@ -668,13 +668,13 @@
     </row>
     <row r="8" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="3">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D8" s="10">
         <v>1</v>
@@ -686,13 +686,13 @@
     </row>
     <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D9" s="10">
         <v>1</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>4</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>2</v>
@@ -736,7 +736,7 @@
     </row>
     <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>2</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>2</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>2</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>2</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="17" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>2</v>
@@ -845,7 +845,7 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>2</v>
